--- a/AAII_Financials/Quarterly/CB_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CB_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="92">
   <si>
     <t>CB</t>
   </si>
@@ -656,316 +656,322 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AP102"/>
+  <dimension ref="A5:AQ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="42" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="43" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44104</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44012</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43921</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43830</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43738</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43646</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43555</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43465</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43373</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43190</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43100</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>43008</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42916</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42825</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42735</v>
       </c>
-      <c r="AP7" s="2">
+      <c r="AQ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>15833000</v>
+      </c>
+      <c r="E8" s="3">
         <v>14781000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>15019000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>16263000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>14925000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>13418000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>14236000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>14907000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>13808000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>13025000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>13034000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>13751000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>11999000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>10899000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>11443000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>12122000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>9901000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>9631000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>10483000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>10845000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>9664000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>9971000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>9848000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>9464000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>8985000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>7697000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>8746000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>9069000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>8540000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>7889000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>7659000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>8761000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>8514000</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>7832000</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>8025000</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>8618000</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>8116000</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>7529000</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>8180000</v>
       </c>
-      <c r="AP8" s="3">
+      <c r="AQ8" s="3">
         <v>8539000</v>
       </c>
     </row>
-    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>10938000</v>
+      </c>
+      <c r="E9" s="3">
         <v>10512000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>10292000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>10886000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>10393000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>10436000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>10042000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>10806000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>9876000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>9114000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>9343000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>10222000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>8529000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>7893000</v>
       </c>
-      <c r="Q9" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R9" s="3" t="s">
         <v>5</v>
       </c>
@@ -1041,53 +1047,56 @@
       <c r="AP9" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AQ9" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>4895000</v>
+      </c>
+      <c r="E10" s="3">
         <v>4269000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>4727000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>5377000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>4532000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>2982000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>4194000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>4101000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>3932000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>3911000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>3691000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>3529000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>3470000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>3006000</v>
       </c>
-      <c r="Q10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R10" s="3" t="s">
         <v>5</v>
       </c>
@@ -1163,8 +1172,11 @@
       <c r="AP10" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AQ10" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1207,8 +1219,9 @@
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
       <c r="AP11" s="3"/>
+      <c r="AQ11" s="3"/>
     </row>
-    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1329,8 +1342,11 @@
       <c r="AP12" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AQ12" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1451,31 +1467,34 @@
       <c r="AP13" s="3">
         <v>0</v>
       </c>
+      <c r="AQ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>8000</v>
+      </c>
+      <c r="E14" s="3">
         <v>9000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>76000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>1000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>2000</v>
       </c>
-      <c r="H14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I14" s="3">
+      <c r="I14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J14" s="3">
         <v>18000</v>
-      </c>
-      <c r="J14" s="3">
-        <v>7000</v>
       </c>
       <c r="K14" s="3">
         <v>7000</v>
@@ -1484,34 +1503,34 @@
         <v>7000</v>
       </c>
       <c r="M14" s="3">
+        <v>7000</v>
+      </c>
+      <c r="N14" s="3">
         <v>-57000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>-102000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>15000</v>
-      </c>
-      <c r="P14" s="3">
-        <v>22000</v>
       </c>
       <c r="Q14" s="3">
         <v>22000</v>
       </c>
       <c r="R14" s="3">
+        <v>22000</v>
+      </c>
+      <c r="S14" s="3">
         <v>23000</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>3000</v>
       </c>
-      <c r="T14" s="3">
-        <v>0</v>
-      </c>
       <c r="U14" s="3">
         <v>0</v>
       </c>
-      <c r="V14" s="3" t="s">
-        <v>5</v>
+      <c r="V14" s="3">
+        <v>0</v>
       </c>
       <c r="W14" s="3" t="s">
         <v>5</v>
@@ -1519,8 +1538,8 @@
       <c r="X14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Y14" s="3">
-        <v>0</v>
+      <c r="Y14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Z14" s="3">
         <v>0</v>
@@ -1532,99 +1551,102 @@
         <v>0</v>
       </c>
       <c r="AC14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD14" s="3">
         <v>22000</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>26000</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>17000</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>16000</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>53000</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>27000</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>17000</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AK14" s="3">
         <v>11000</v>
       </c>
-      <c r="AK14" s="3">
+      <c r="AL14" s="3">
         <v>87000</v>
       </c>
-      <c r="AL14" s="3">
+      <c r="AM14" s="3">
         <v>58000</v>
       </c>
-      <c r="AM14" s="3">
+      <c r="AN14" s="3">
         <v>80000</v>
       </c>
-      <c r="AN14" s="3">
+      <c r="AO14" s="3">
         <v>130000</v>
       </c>
-      <c r="AO14" s="3">
+      <c r="AP14" s="3">
         <v>143000</v>
       </c>
-      <c r="AP14" s="3">
+      <c r="AQ14" s="3">
         <v>127000</v>
       </c>
     </row>
-    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>74000</v>
+      </c>
+      <c r="E15" s="3">
         <v>73000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>77000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>75000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>74000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>75000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>82000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>81000</v>
-      </c>
-      <c r="K15" s="3">
-        <v>80000</v>
       </c>
       <c r="L15" s="3">
         <v>80000</v>
       </c>
       <c r="M15" s="3">
-        <v>84000</v>
+        <v>80000</v>
       </c>
       <c r="N15" s="3">
         <v>84000</v>
       </c>
       <c r="O15" s="3">
+        <v>84000</v>
+      </c>
+      <c r="P15" s="3">
         <v>70000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>72000</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>74000</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>69000</v>
-      </c>
-      <c r="S15" s="3">
-        <v>71000</v>
       </c>
       <c r="T15" s="3">
         <v>71000</v>
@@ -1636,67 +1658,70 @@
         <v>71000</v>
       </c>
       <c r="W15" s="3">
+        <v>71000</v>
+      </c>
+      <c r="X15" s="3">
         <v>73000</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>72000</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>73000</v>
-      </c>
-      <c r="Z15" s="3">
-        <v>72000</v>
       </c>
       <c r="AA15" s="3">
         <v>72000</v>
       </c>
       <c r="AB15" s="3">
+        <v>72000</v>
+      </c>
+      <c r="AC15" s="3">
         <v>73000</v>
-      </c>
-      <c r="AC15" s="3">
-        <v>76000</v>
       </c>
       <c r="AD15" s="3">
         <v>76000</v>
       </c>
       <c r="AE15" s="3">
+        <v>76000</v>
+      </c>
+      <c r="AF15" s="3">
         <v>77000</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>76000</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>86000</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>83000</v>
-      </c>
-      <c r="AI15" s="3">
-        <v>85000</v>
       </c>
       <c r="AJ15" s="3">
         <v>85000</v>
       </c>
       <c r="AK15" s="3">
+        <v>85000</v>
+      </c>
+      <c r="AL15" s="3">
         <v>66000</v>
-      </c>
-      <c r="AL15" s="3">
-        <v>65000</v>
       </c>
       <c r="AM15" s="3">
         <v>65000</v>
       </c>
       <c r="AN15" s="3">
+        <v>65000</v>
+      </c>
+      <c r="AO15" s="3">
         <v>64000</v>
       </c>
-      <c r="AO15" s="3">
+      <c r="AP15" s="3">
         <v>3000</v>
       </c>
-      <c r="AP15" s="3">
+      <c r="AQ15" s="3">
         <v>4000</v>
       </c>
     </row>
-    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1736,252 +1761,259 @@
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
       <c r="AP16" s="3"/>
+      <c r="AQ16" s="3"/>
     </row>
-    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>12108000</v>
+      </c>
+      <c r="E17" s="3">
         <v>11730000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>11378000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>12096000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>11594000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>11590000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>11195000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>11999000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>11034000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>10257000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>10502000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>11309000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>9568000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>8912000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>9554000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>10721000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>8190000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>7509000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>8151000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>9440000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>7742000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>7706000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>7598000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>8487000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>9198000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>7049000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>7546000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>7672000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>7278000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>6566000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>7117000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>7335000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>6954000</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>6508000</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>6846000</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>8747000</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>6624000</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>6227000</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>6298000</v>
       </c>
-      <c r="AP17" s="3">
+      <c r="AQ17" s="3">
         <v>6843000</v>
       </c>
     </row>
-    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>3725000</v>
+      </c>
+      <c r="E18" s="3">
         <v>3051000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>3641000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>4167000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>3331000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>1828000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>3041000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>2908000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>2774000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>2768000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>2532000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>2442000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>2431000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>1987000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>1889000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>1401000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>1711000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>2122000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>2332000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>1405000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>1922000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>2265000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>2250000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>977000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-213000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>648000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>1200000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>1397000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>1262000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>1323000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>542000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>1426000</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>1560000</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>1324000</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>1179000</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>-129000</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>1492000</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>1302000</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>1882000</v>
       </c>
-      <c r="AP18" s="3">
+      <c r="AQ18" s="3">
         <v>1696000</v>
       </c>
     </row>
-    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -2024,311 +2056,318 @@
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
       <c r="AP19" s="3"/>
+      <c r="AQ19" s="3"/>
     </row>
-    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-107000</v>
+      </c>
+      <c r="E20" s="3">
         <v>-149000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-410000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>75000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-568000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-17000</v>
-      </c>
-      <c r="I20" s="3">
-        <v>-285000</v>
       </c>
       <c r="J20" s="3">
         <v>-285000</v>
       </c>
       <c r="K20" s="3">
+        <v>-285000</v>
+      </c>
+      <c r="L20" s="3">
         <v>-121000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-53000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-196000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-83000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>66000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-471000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-92000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-196000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-96000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>316000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>339000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>768000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>782000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>495000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>628000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>489000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-52000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-49000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>276000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>62000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>236000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>45000</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>125000</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>152000</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>119000</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>50000</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>128000</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>124000</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>160000</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>73000</v>
       </c>
-      <c r="AO20" s="3">
+      <c r="AP20" s="3">
         <v>141000</v>
       </c>
-      <c r="AP20" s="3">
+      <c r="AQ20" s="3">
         <v>93000</v>
       </c>
     </row>
-    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>3906000</v>
+      </c>
+      <c r="E21" s="3">
         <v>3273000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>4128000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>4167000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>3973000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>1920000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>3408000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>3274000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>2975000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>2901000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>2812000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>2609000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>2435000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>2530000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>1871000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>1274000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>1686000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>2509000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>2742000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>2244000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>2777000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>2832000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>2951000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>1538000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-193000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>672000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>1552000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>1535000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>1575000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>1444000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>753000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>1661000</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>1764000</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>1459000</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>1373000</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>60000</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>1717000</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>1439000</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <v>2022000</v>
       </c>
-      <c r="AP21" s="3">
+      <c r="AQ21" s="3">
         <v>1788000</v>
       </c>
     </row>
-    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>200000</v>
+      </c>
+      <c r="E22" s="3">
         <v>198000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>205000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>197000</v>
-      </c>
-      <c r="G22" s="3">
-        <v>181000</v>
       </c>
       <c r="H22" s="3">
         <v>181000</v>
       </c>
       <c r="I22" s="3">
+        <v>181000</v>
+      </c>
+      <c r="J22" s="3">
         <v>189000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>192000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>182000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>178000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>173000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>174000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>165000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>160000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>154000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>150000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>134000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>132000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>126000</v>
-      </c>
-      <c r="V22" s="3">
-        <v>122000</v>
       </c>
       <c r="W22" s="3">
         <v>122000</v>
@@ -2337,305 +2376,314 @@
         <v>122000</v>
       </c>
       <c r="Y22" s="3">
+        <v>122000</v>
+      </c>
+      <c r="Z22" s="3">
         <v>126000</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>130000</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>128000</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>132000</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>134000</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>138000</v>
-      </c>
-      <c r="AE22" s="3">
-        <v>140000</v>
       </c>
       <c r="AF22" s="3">
         <v>140000</v>
       </c>
       <c r="AG22" s="3">
+        <v>140000</v>
+      </c>
+      <c r="AH22" s="3">
         <v>153000</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>164000</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>167000</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>157000</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>156000</v>
       </c>
-      <c r="AL22" s="3">
+      <c r="AM22" s="3">
         <v>150000</v>
       </c>
-      <c r="AM22" s="3">
+      <c r="AN22" s="3">
         <v>147000</v>
-      </c>
-      <c r="AN22" s="3">
-        <v>154000</v>
       </c>
       <c r="AO22" s="3">
         <v>154000</v>
       </c>
       <c r="AP22" s="3">
+        <v>154000</v>
+      </c>
+      <c r="AQ22" s="3">
         <v>152000</v>
       </c>
     </row>
-    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>3624000</v>
+      </c>
+      <c r="E23" s="3">
         <v>2993000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>3770000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>3894000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>3716000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>1664000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>3119000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>2994000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>2706000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>2636000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>2612000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>2453000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>2185000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>2276000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>1643000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>1055000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>1481000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>2306000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>2545000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>2051000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>2582000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>2638000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>2752000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>1336000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-393000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>467000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>1342000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>1321000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>1358000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>1228000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>514000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>1414000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>1512000</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>1217000</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>1151000</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>-155000</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>1505000</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>1221000</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>1869000</v>
       </c>
-      <c r="AP23" s="3">
+      <c r="AQ23" s="3">
         <v>1637000</v>
       </c>
     </row>
-    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>742000</v>
+      </c>
+      <c r="E24" s="3">
         <v>646000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>597000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>787000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>717000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>321000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>479000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>504000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>490000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>342000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-678000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>413000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>392000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>384000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>332000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>263000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>291000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>353000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>404000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>218000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>317000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>338000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>334000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>142000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>-62000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>215000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>169000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>230000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>208000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>188000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>184000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>183000</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>218000</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>135000</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>68000</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>-85000</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>200000</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>128000</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>259000</v>
       </c>
-      <c r="AP24" s="3">
+      <c r="AQ24" s="3">
         <v>277000</v>
       </c>
     </row>
-    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2756,252 +2804,261 @@
       <c r="AP25" s="3">
         <v>0</v>
       </c>
+      <c r="AQ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>2882000</v>
+      </c>
+      <c r="E26" s="3">
         <v>2347000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>3173000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>3107000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>2999000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>1343000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>2640000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>2490000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>2216000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>2294000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>3290000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>2040000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>1793000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>1892000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>1311000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>792000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>1190000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>1953000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>2141000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>1833000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>2265000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>2300000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>2418000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>1194000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-331000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>252000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>1173000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>1091000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>1150000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>1040000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>330000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>1231000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>1294000</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>1082000</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>1083000</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>-70000</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>1305000</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>1093000</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>1610000</v>
       </c>
-      <c r="AP26" s="3">
+      <c r="AQ26" s="3">
         <v>1360000</v>
       </c>
     </row>
-    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>2854000</v>
+      </c>
+      <c r="E27" s="3">
         <v>2320000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>3210000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>2801000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>2968000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>1331000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>2575000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>2324000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>2230000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>2143000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>3300000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>2043000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>1793000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>1892000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>1311000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>792000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>1190000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>1953000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>2141000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>1833000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>2265000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>2300000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>2418000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>1194000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-331000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>252000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>1173000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>1091000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>1150000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>1040000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>330000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>1231000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>1294000</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>1082000</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>1083000</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>-70000</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>1305000</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>1093000</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>1610000</v>
       </c>
-      <c r="AP27" s="3">
+      <c r="AQ27" s="3">
         <v>1360000</v>
       </c>
     </row>
-    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3122,8 +3179,11 @@
       <c r="AP28" s="3">
         <v>0</v>
       </c>
+      <c r="AQ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3196,8 +3256,8 @@
       <c r="Z29" s="3">
         <v>0</v>
       </c>
-      <c r="AA29" s="3" t="s">
-        <v>5</v>
+      <c r="AA29" s="3">
+        <v>0</v>
       </c>
       <c r="AB29" s="3" t="s">
         <v>5</v>
@@ -3214,24 +3274,24 @@
       <c r="AF29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AG29" s="3">
+      <c r="AG29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH29" s="3">
         <v>25000</v>
       </c>
-      <c r="AH29" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AI29" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AJ29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AK29" s="3">
+      <c r="AK29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL29" s="3">
         <v>450000</v>
       </c>
-      <c r="AL29" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AM29" s="3" t="s">
         <v>5</v>
       </c>
@@ -3244,8 +3304,11 @@
       <c r="AP29" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AQ29" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3366,8 +3429,11 @@
       <c r="AP30" s="3">
         <v>0</v>
       </c>
+      <c r="AQ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3488,252 +3554,261 @@
       <c r="AP31" s="3">
         <v>0</v>
       </c>
+      <c r="AQ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>107000</v>
+      </c>
+      <c r="E32" s="3">
         <v>149000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>410000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-75000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>568000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>17000</v>
-      </c>
-      <c r="I32" s="3">
-        <v>285000</v>
       </c>
       <c r="J32" s="3">
         <v>285000</v>
       </c>
       <c r="K32" s="3">
+        <v>285000</v>
+      </c>
+      <c r="L32" s="3">
         <v>121000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>53000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>196000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>83000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-66000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>471000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>92000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>196000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>96000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-316000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-339000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-768000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-782000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-495000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-628000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-489000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>52000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>49000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-276000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-62000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-236000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-45000</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-125000</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-152000</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-119000</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-50000</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>-128000</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>-124000</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>-160000</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>-73000</v>
       </c>
-      <c r="AO32" s="3">
+      <c r="AP32" s="3">
         <v>-141000</v>
       </c>
-      <c r="AP32" s="3">
+      <c r="AQ32" s="3">
         <v>-93000</v>
       </c>
     </row>
-    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>2854000</v>
+      </c>
+      <c r="E33" s="3">
         <v>2320000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>3210000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>2801000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>2968000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>1331000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>2575000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>2324000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>2230000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>2143000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>3300000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>2043000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>1793000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>1892000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>1311000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>792000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>1190000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>1953000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>2141000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>1833000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>2265000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>2300000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>2418000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>1194000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-331000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>252000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>1173000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>1091000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>1150000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>1040000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>355000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>1231000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>1294000</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>1082000</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>1533000</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>-70000</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>1305000</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>1093000</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>1610000</v>
       </c>
-      <c r="AP33" s="3">
+      <c r="AQ33" s="3">
         <v>1360000</v>
       </c>
     </row>
-    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3854,257 +3929,266 @@
       <c r="AP34" s="3">
         <v>0</v>
       </c>
+      <c r="AQ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>2854000</v>
+      </c>
+      <c r="E35" s="3">
         <v>2320000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>3210000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>2801000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>2968000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>1331000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>2575000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>2324000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>2230000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>2143000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>3300000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>2043000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>1793000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>1892000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>1311000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>792000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>1190000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>1953000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>2141000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>1833000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>2265000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>2300000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>2418000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>1194000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-331000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>252000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>1173000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>1091000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>1150000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>1040000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>355000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>1231000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>1294000</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>1082000</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>1533000</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>-70000</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>1305000</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>1093000</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>1610000</v>
       </c>
-      <c r="AP35" s="3">
+      <c r="AQ35" s="3">
         <v>1360000</v>
       </c>
     </row>
-    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44104</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44012</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43921</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43830</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43738</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43646</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43555</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43465</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43373</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43190</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43100</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>43008</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42916</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42825</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42735</v>
       </c>
-      <c r="AP38" s="2">
+      <c r="AQ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4147,8 +4231,9 @@
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
       <c r="AP39" s="3"/>
+      <c r="AQ39" s="3"/>
     </row>
-    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4191,175 +4276,179 @@
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
       <c r="AP40" s="3"/>
+      <c r="AQ40" s="3"/>
     </row>
-    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>2510000</v>
+      </c>
+      <c r="E41" s="3">
         <v>2431000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>2272000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>2241000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>2189000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1972000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>2288000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>2525000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>2400000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>2508000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>2449000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>2586000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>2285000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>2288000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>2012000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>2128000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>7122000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>1734000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>1659000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>1620000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>1843000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>1684000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>1747000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>1707000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>1557000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>1512000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>1537000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>1478000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>1270000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>1271000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>1247000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>1053000</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>1000000</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>1988000</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>728000</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>1088000</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>1297000</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>1063000</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>985000</v>
       </c>
-      <c r="AP41" s="3">
+      <c r="AQ41" s="3">
         <v>870000</v>
       </c>
     </row>
-    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>5458000</v>
+      </c>
+      <c r="E42" s="3">
         <v>5067000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>4840000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>4380000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>4508000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>4432000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>5142000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>4375000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>4546000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>5107000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>4551000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>5454000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>4097000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>3693000</v>
       </c>
-      <c r="Q42" s="3">
-        <v>0</v>
-      </c>
       <c r="R42" s="3">
         <v>0</v>
       </c>
@@ -4435,130 +4524,136 @@
       <c r="AP42" s="3">
         <v>0</v>
       </c>
+      <c r="AQ42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>19068000</v>
+      </c>
+      <c r="E43" s="3">
         <v>17101000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>16363000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>16305000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>16778000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>15358000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>14672000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>15709000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>15929000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>13991000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>13645000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>13907000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>14128000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>12340000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>11933000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>12853000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>12758000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>11452000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>11322000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>11723000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>11720000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>10573000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>10480000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>10588000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>10853000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>10058000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>10357000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>10403000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>10935000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>9826000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>10075000</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>10193000</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>10341000</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>9570000</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>9334000</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>9551000</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>9662000</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>8880000</v>
       </c>
-      <c r="AO43" s="3">
+      <c r="AP43" s="3">
         <v>8970000</v>
       </c>
-      <c r="AP43" s="3">
+      <c r="AQ43" s="3">
         <v>8493000</v>
       </c>
     </row>
-    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4601,8 +4696,8 @@
       <c r="P44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q44" s="3">
-        <v>0</v>
+      <c r="Q44" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="R44" s="3">
         <v>0</v>
@@ -4679,53 +4774,56 @@
       <c r="AP44" s="3">
         <v>0</v>
       </c>
+      <c r="AQ44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>22509000</v>
+      </c>
+      <c r="E45" s="3">
         <v>22135000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>22228000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>22244000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>21531000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>21655000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>21448000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>21255000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>20945000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>20649000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>21508000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>21248000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>19797000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>19437000</v>
       </c>
-      <c r="Q45" s="3">
-        <v>0</v>
-      </c>
       <c r="R45" s="3">
         <v>0</v>
       </c>
@@ -4801,53 +4899,56 @@
       <c r="AP45" s="3">
         <v>0</v>
       </c>
+      <c r="AQ45" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>54471000</v>
+      </c>
+      <c r="E46" s="3">
         <v>51042000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>49775000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>49557000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>49482000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>47376000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>47189000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>47665000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>47735000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>45639000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>45546000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>46901000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>43996000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>41018000</v>
       </c>
-      <c r="Q46" s="3">
-        <v>0</v>
-      </c>
       <c r="R46" s="3">
         <v>0</v>
       </c>
@@ -4923,223 +5024,229 @@
       <c r="AP46" s="3">
         <v>0</v>
       </c>
+      <c r="AQ46" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>167191000</v>
+      </c>
+      <c r="E47" s="3">
         <v>165128000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>162169000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>161616000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>153806000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>147869000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>144049000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>145733000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>135161000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>134527000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>131070000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>124695000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>116081000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>115651000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>116058000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>114683000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>112851000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>121408000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>125453000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>125135000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>124353000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>121850000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>121482000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>118581000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>112241000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>106630000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>110566000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>108242000</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>106789000</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>103968000</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>101646000</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>101819000</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>101861000</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>102769000</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>103106000</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>103076000</v>
       </c>
-      <c r="AM47" s="3">
+      <c r="AN47" s="3">
         <v>100870000</v>
       </c>
-      <c r="AN47" s="3">
+      <c r="AO47" s="3">
         <v>100157000</v>
       </c>
-      <c r="AO47" s="3">
+      <c r="AP47" s="3">
         <v>99760000</v>
       </c>
-      <c r="AP47" s="3">
+      <c r="AQ47" s="3">
         <v>101701000</v>
       </c>
     </row>
-    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1002000</v>
+      </c>
+      <c r="E48" s="3">
         <v>1001000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>4525000</v>
-      </c>
-      <c r="F48" s="3">
-        <v>1044000</v>
       </c>
       <c r="G48" s="3">
         <v>1044000</v>
       </c>
       <c r="H48" s="3">
+        <v>1044000</v>
+      </c>
+      <c r="I48" s="3">
         <v>1052000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>3924000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>748000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>743000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>762000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>3684000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>549000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>543000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>571000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>607000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>458000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>433000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>437000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>445000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>434000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>429000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>448000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>473000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>470000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>483000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>509000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>551000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>577000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>601000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>608000</v>
       </c>
-      <c r="AG48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AH48" s="3" t="s">
         <v>5</v>
       </c>
@@ -5149,8 +5256,8 @@
       <c r="AJ48" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AK48" s="3">
-        <v>0</v>
+      <c r="AK48" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AL48" s="3">
         <v>0</v>
@@ -5167,130 +5274,136 @@
       <c r="AP48" s="3">
         <v>0</v>
       </c>
+      <c r="AQ48" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>40060000</v>
+      </c>
+      <c r="E49" s="3">
         <v>39965000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>41631000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>39508000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>39257000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>37988000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>37537000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>38285000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>37698000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>37559000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>37287000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>36929000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>31883000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>31438000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>21669000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>21490000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>20317000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>20643000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>20668000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>20965000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>21200000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>21161000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>21211000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>21103000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>21093000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>20873000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>21359000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>21378000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>21566000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>21419000</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>21414000</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>21471000</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>21759000</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>22123000</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>22054000</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>22265000</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>22013000</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>22061000</v>
       </c>
-      <c r="AO49" s="3">
+      <c r="AP49" s="3">
         <v>22095000</v>
       </c>
-      <c r="AP49" s="3">
+      <c r="AQ49" s="3">
         <v>22472000</v>
       </c>
     </row>
-    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5411,8 +5524,11 @@
       <c r="AP50" s="3">
         <v>0</v>
       </c>
+      <c r="AQ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5533,113 +5649,116 @@
       <c r="AP51" s="3">
         <v>0</v>
       </c>
+      <c r="AQ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>17361000</v>
+      </c>
+      <c r="E52" s="3">
         <v>17005000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>11798000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>17072000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>16353000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>15669000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>11305000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>15444000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>14495000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>13883000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>10703000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>13674000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>12945000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>12737000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>115000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>136000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>681000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>513000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>152000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>176000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>155000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>157000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>89000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>166000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>152000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>146000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>109000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>111000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>98000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>122000</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>93000</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>104000</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>101000</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>125000</v>
       </c>
-      <c r="AK52" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AL52" s="3" t="s">
         <v>5</v>
       </c>
@@ -5649,14 +5768,17 @@
       <c r="AN52" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AO52" s="3">
-        <v>0</v>
+      <c r="AO52" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AP52" s="3">
         <v>0</v>
       </c>
+      <c r="AQ52" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5777,130 +5899,136 @@
       <c r="AP53" s="3">
         <v>0</v>
       </c>
+      <c r="AQ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>281322000</v>
+      </c>
+      <c r="E54" s="3">
         <v>275456000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>272327000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>270210000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>261563000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>251752000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>246548000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>250557000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>238551000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>234867000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>230682000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>222748000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>205448000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>201415000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>199017000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>198111000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>195651000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>197990000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>200054000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>199054000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>197174000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>191977000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>190774000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>187786000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>181474000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>173127000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>176943000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>175148000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>174516000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>171347000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>167771000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>167684000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>167534000</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>168781000</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>167022000</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>167578000</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>162988000</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>160967000</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>159786000</v>
       </c>
-      <c r="AP54" s="3">
+      <c r="AQ54" s="3">
         <v>161810000</v>
       </c>
     </row>
-    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5943,8 +6071,9 @@
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
       <c r="AP55" s="3"/>
+      <c r="AQ55" s="3"/>
     </row>
-    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5987,201 +6116,205 @@
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
       <c r="AP56" s="3"/>
+      <c r="AQ56" s="3"/>
     </row>
-    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>98000000</v>
+      </c>
+      <c r="E57" s="3">
         <v>97565000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>96544000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>96466000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>94247000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>93107000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>92964000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>92145000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>89165000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>87598000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>87070000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>87310000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>82528000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>81191000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>6515000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>16187000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>14055000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>14444000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>14520000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>14998000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>14116000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>13561000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>13535000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>12557000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>12058000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>11351000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>11064000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>11487000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>10823000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>10298000</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>10472000</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>9343000</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>8933000</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>8618000</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>9545000</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>9173000</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>8952000</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>9073000</v>
       </c>
-      <c r="AO57" s="3">
+      <c r="AP57" s="3">
         <v>8617000</v>
       </c>
-      <c r="AP57" s="3">
+      <c r="AQ57" s="3">
         <v>9748000</v>
       </c>
     </row>
-    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>5901000</v>
+      </c>
+      <c r="E58" s="3">
         <v>7513000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>7533000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>6758000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>6499000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>5033000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>4976000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>6546000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>6591000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>6995000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>5592000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>4786000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>3742000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>3002000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>475000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>1475000</v>
-      </c>
-      <c r="S58" s="3">
-        <v>1474000</v>
       </c>
       <c r="T58" s="3">
         <v>1474000</v>
       </c>
       <c r="U58" s="3">
+        <v>1474000</v>
+      </c>
+      <c r="V58" s="3">
         <v>999000</v>
       </c>
-      <c r="V58" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="W58" s="3" t="s">
         <v>5</v>
       </c>
       <c r="X58" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Y58" s="3">
-        <v>0</v>
+      <c r="Y58" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Z58" s="3">
-        <v>1300000</v>
+        <v>0</v>
       </c>
       <c r="AA58" s="3">
         <v>1300000</v>
@@ -6190,216 +6323,222 @@
         <v>1300000</v>
       </c>
       <c r="AC58" s="3">
+        <v>1300000</v>
+      </c>
+      <c r="AD58" s="3">
         <v>1299000</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>10000</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>9000</v>
-      </c>
-      <c r="AF58" s="3">
-        <v>509000</v>
       </c>
       <c r="AG58" s="3">
         <v>509000</v>
       </c>
       <c r="AH58" s="3">
+        <v>509000</v>
+      </c>
+      <c r="AI58" s="3">
         <v>500000</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>600000</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>1669000</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>1013000</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>1020000</v>
       </c>
-      <c r="AM58" s="3">
+      <c r="AN58" s="3">
         <v>922000</v>
       </c>
-      <c r="AN58" s="3">
+      <c r="AO58" s="3">
         <v>300000</v>
-      </c>
-      <c r="AO58" s="3">
-        <v>500000</v>
       </c>
       <c r="AP58" s="3">
         <v>500000</v>
       </c>
+      <c r="AQ58" s="3">
+        <v>500000</v>
+      </c>
     </row>
-    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>29011000</v>
+      </c>
+      <c r="E59" s="3">
         <v>27180000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>26757000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>27333000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>26921000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>24887000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>23925000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>24829000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>24374000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>23010000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>22687000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>22924000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>22101000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>20548000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>49874000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>42464000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>39744000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>36637000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>36012000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>36759000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>36864000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>34416000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>33839000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>33658000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>32997000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>30041000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>30885000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>30710000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>31312000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>31122000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>29958000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>30605000</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>30937000</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>29977000</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>29000000</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>29120000</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>28094000</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>27030000</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AP59" s="3">
         <v>27095000</v>
       </c>
-      <c r="AP59" s="3">
+      <c r="AQ59" s="3">
         <v>28662000</v>
       </c>
     </row>
-    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>132912000</v>
+      </c>
+      <c r="E60" s="3">
         <v>132258000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>130834000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>130557000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>127667000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>123027000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>121865000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>123520000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>120130000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>117603000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>115349000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>115020000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>108371000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>104741000</v>
       </c>
-      <c r="Q60" s="3">
-        <v>0</v>
-      </c>
       <c r="R60" s="3">
         <v>0</v>
       </c>
@@ -6475,252 +6614,261 @@
       <c r="AP60" s="3">
         <v>0</v>
       </c>
+      <c r="AQ60" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>19113000</v>
+      </c>
+      <c r="E61" s="3">
         <v>17626000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>17154000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>17331000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>15074000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>16104000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>15740000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>15686000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>14288000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>14375000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>14175000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>14621000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>14665000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>15278000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>14710000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>14352000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>14619000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>14893000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>15477000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>15131000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>15262000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>15187000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>15256000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>15138000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>13964000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>13818000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>13867000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>13593000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>13679000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>12379000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>12395000</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>12457000</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>12492000</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>13094000</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>11864000</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>11867000</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>11975000</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>12608000</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AP61" s="3">
         <v>12918000</v>
       </c>
-      <c r="AP61" s="3">
+      <c r="AQ61" s="3">
         <v>12929000</v>
       </c>
     </row>
-    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>46582000</v>
+      </c>
+      <c r="E62" s="3">
         <v>43901000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>42819000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>42778000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>42684000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>40258000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>38965000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>39579000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>37986000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>36915000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>35912000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>34844000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>29004000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>27868000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>377000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>2000</v>
       </c>
-      <c r="S62" s="3">
-        <v>0</v>
-      </c>
       <c r="T62" s="3">
         <v>0</v>
       </c>
       <c r="U62" s="3">
+        <v>0</v>
+      </c>
+      <c r="V62" s="3">
         <v>389000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>217000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>581000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>482000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>892000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>815000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>696000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>474000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>804000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>766000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>697000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>541000</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>304000</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>363000</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>326000</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>468000</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>699000</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>1139000</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>1122000</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>967000</v>
       </c>
-      <c r="AO62" s="3">
+      <c r="AP62" s="3">
         <v>988000</v>
       </c>
-      <c r="AP62" s="3">
+      <c r="AQ62" s="3">
         <v>1418000</v>
       </c>
     </row>
-    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6841,8 +6989,11 @@
       <c r="AP63" s="3">
         <v>0</v>
       </c>
+      <c r="AQ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6963,8 +7114,11 @@
       <c r="AP64" s="3">
         <v>0</v>
       </c>
+      <c r="AQ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -7085,130 +7239,136 @@
       <c r="AP65" s="3">
         <v>0</v>
       </c>
+      <c r="AQ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>200477000</v>
+      </c>
+      <c r="E66" s="3">
         <v>195544000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>192548000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>192399000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>187116000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>180997000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>178154000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>180437000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>173976000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>170436000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>166991000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>165244000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>152573000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>148428000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>148498000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>150472000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>143984000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>141292000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>140340000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>139736000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>137112000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>132901000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>131333000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>131373000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>126714000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>120930000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>121612000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>120576000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>120714000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>118992000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>117459000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>116750000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>116563000</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>117494000</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>115850000</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>117107000</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>112639000</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>111743000</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>111511000</v>
       </c>
-      <c r="AP66" s="3">
+      <c r="AQ66" s="3">
         <v>113438000</v>
       </c>
     </row>
-    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7251,8 +7411,9 @@
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
       <c r="AP67" s="3"/>
+      <c r="AQ67" s="3"/>
     </row>
-    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7373,8 +7534,11 @@
       <c r="AP68" s="3">
         <v>0</v>
       </c>
+      <c r="AQ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7495,8 +7659,11 @@
       <c r="AP69" s="3">
         <v>0</v>
       </c>
+      <c r="AQ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7617,8 +7784,11 @@
       <c r="AP70" s="3">
         <v>0</v>
       </c>
+      <c r="AQ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7739,130 +7909,136 @@
       <c r="AP71" s="3">
         <v>0</v>
       </c>
+      <c r="AQ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>71675000</v>
+      </c>
+      <c r="E72" s="3">
         <v>68821000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>69950000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>66722000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>63921000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>60953000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>61561000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>58986000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>56662000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>56953000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>54810000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>51510000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>49467000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>50197000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>48305000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>47022000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>48363000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>47148000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>47365000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>45224000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>43902000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>41637000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>39337000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>36919000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>35991000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>36331000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>36142000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>34969000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>33878000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>32728000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>31700000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>31491000</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>30260000</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>28965000</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>27474000</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>25941000</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>26011000</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>24706000</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>23613000</v>
       </c>
-      <c r="AP72" s="3">
+      <c r="AQ72" s="3">
         <v>22003000</v>
       </c>
     </row>
-    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7983,8 +8159,11 @@
       <c r="AP73" s="3">
         <v>0</v>
       </c>
+      <c r="AQ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -8105,8 +8284,11 @@
       <c r="AP74" s="3">
         <v>0</v>
       </c>
+      <c r="AQ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8227,130 +8409,136 @@
       <c r="AP75" s="3">
         <v>0</v>
       </c>
+      <c r="AQ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>75372000</v>
+      </c>
+      <c r="E76" s="3">
         <v>73788000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>73757000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>71855000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>69395000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>65726000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>64021000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>65757000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>61038000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>60535000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>59507000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>52373000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>52875000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>52987000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>50519000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>47639000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>51667000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>56698000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>59714000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>59318000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>60062000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>59076000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>59441000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>56413000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>54760000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>52197000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>55331000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>54572000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>53802000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>52355000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>50312000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>50934000</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>50971000</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>51287000</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>51172000</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>50471000</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>50349000</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>49224000</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>48275000</v>
       </c>
-      <c r="AP76" s="3">
+      <c r="AQ76" s="3">
         <v>48372000</v>
       </c>
     </row>
-    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8471,257 +8659,266 @@
       <c r="AP77" s="3">
         <v>0</v>
       </c>
+      <c r="AQ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44104</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44012</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43921</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43830</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43738</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43646</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43555</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43465</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43373</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43190</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43100</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>43008</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42916</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42825</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42735</v>
       </c>
-      <c r="AP80" s="2">
+      <c r="AQ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>2854000</v>
+      </c>
+      <c r="E81" s="3">
         <v>2320000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>3210000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>2801000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>2968000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>1331000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>2575000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>2324000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>2230000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>2143000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>3300000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>2043000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>1793000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>1892000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>1311000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>792000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>1190000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>1953000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>2141000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>1833000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>2265000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>2300000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>2418000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>1194000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-331000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>252000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>1173000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>1091000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>1150000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>1040000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>355000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>1231000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>1294000</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>1082000</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>1533000</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>-70000</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>1305000</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>1093000</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>1610000</v>
       </c>
-      <c r="AP81" s="3">
+      <c r="AQ81" s="3">
         <v>1360000</v>
       </c>
     </row>
-    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8764,8 +8961,9 @@
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
       <c r="AP82" s="3"/>
+      <c r="AQ82" s="3"/>
     </row>
-    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -8808,14 +9006,14 @@
       <c r="P83" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="Q83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R83" s="3">
         <v>74000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>69000</v>
-      </c>
-      <c r="S83" s="3">
-        <v>71000</v>
       </c>
       <c r="T83" s="3">
         <v>71000</v>
@@ -8827,67 +9025,70 @@
         <v>71000</v>
       </c>
       <c r="W83" s="3">
+        <v>71000</v>
+      </c>
+      <c r="X83" s="3">
         <v>73000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>72000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>73000</v>
-      </c>
-      <c r="Z83" s="3">
-        <v>72000</v>
       </c>
       <c r="AA83" s="3">
         <v>72000</v>
       </c>
       <c r="AB83" s="3">
+        <v>72000</v>
+      </c>
+      <c r="AC83" s="3">
         <v>73000</v>
-      </c>
-      <c r="AC83" s="3">
-        <v>76000</v>
       </c>
       <c r="AD83" s="3">
         <v>76000</v>
       </c>
       <c r="AE83" s="3">
+        <v>76000</v>
+      </c>
+      <c r="AF83" s="3">
         <v>77000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>76000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>86000</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>83000</v>
-      </c>
-      <c r="AI83" s="3">
-        <v>85000</v>
       </c>
       <c r="AJ83" s="3">
         <v>85000</v>
       </c>
       <c r="AK83" s="3">
+        <v>85000</v>
+      </c>
+      <c r="AL83" s="3">
         <v>66000</v>
-      </c>
-      <c r="AL83" s="3">
-        <v>65000</v>
       </c>
       <c r="AM83" s="3">
         <v>65000</v>
       </c>
       <c r="AN83" s="3">
+        <v>65000</v>
+      </c>
+      <c r="AO83" s="3">
         <v>64000</v>
       </c>
-      <c r="AO83" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AP83" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AQ83" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -9008,8 +9209,11 @@
       <c r="AP84" s="3">
         <v>0</v>
       </c>
+      <c r="AQ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -9130,8 +9334,11 @@
       <c r="AP85" s="3">
         <v>0</v>
       </c>
+      <c r="AQ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9252,8 +9459,11 @@
       <c r="AP86" s="3">
         <v>0</v>
       </c>
+      <c r="AQ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9374,8 +9584,11 @@
       <c r="AP87" s="3">
         <v>0</v>
       </c>
+      <c r="AQ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9496,130 +9709,136 @@
       <c r="AP88" s="3">
         <v>0</v>
       </c>
+      <c r="AQ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>3730000</v>
+      </c>
+      <c r="E89" s="3">
         <v>3947000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>4060000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>3639000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>3551000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>1566000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>4565000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>4318000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>4079000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>3220000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>3186000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>4680000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>2515000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>2251000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>2666000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>3432000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>2720000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>2440000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>2600000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>3322000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>3122000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>2105000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>2544000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>3544000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>1985000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>1712000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>1429000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>2205000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>1386000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>1322000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>1583000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>1700000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>1646000</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>551000</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>1092000</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>1771000</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>627000</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>1013000</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>1455000</v>
       </c>
-      <c r="AP89" s="3">
+      <c r="AQ89" s="3">
         <v>1684000</v>
       </c>
     </row>
-    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9662,8 +9881,9 @@
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
       <c r="AP90" s="3"/>
+      <c r="AQ90" s="3"/>
     </row>
-    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -9706,8 +9926,8 @@
       <c r="P91" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q91" s="3">
-        <v>0</v>
+      <c r="Q91" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="R91" s="3">
         <v>0</v>
@@ -9784,8 +10004,11 @@
       <c r="AP91" s="3">
         <v>0</v>
       </c>
+      <c r="AQ91" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9906,8 +10129,11 @@
       <c r="AP92" s="3">
         <v>0</v>
       </c>
+      <c r="AQ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -10028,130 +10254,136 @@
       <c r="AP93" s="3">
         <v>0</v>
       </c>
+      <c r="AQ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-2342000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-2835000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-2332000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-5303000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-2827000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-798000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-2474000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-5383000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-2320000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-3746000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-2214000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-3172000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-1692000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-570000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-452000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-6327000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>2120000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-995000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-2908000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-1726000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-773000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-1252000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-792000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-4035000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-1684000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-1010000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-2344000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-1274000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-1614000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-673000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-808000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-867000</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-379000</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-881000</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-1081000</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-1464000</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>183000</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-60000</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>-1041000</v>
       </c>
-      <c r="AP94" s="3">
+      <c r="AQ94" s="3">
         <v>-1602000</v>
       </c>
     </row>
-    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -10194,130 +10426,134 @@
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
       <c r="AP95" s="3"/>
+      <c r="AQ95" s="3"/>
     </row>
-    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>379000</v>
+      </c>
+      <c r="E96" s="3">
         <v>380000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>384000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>390000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>365000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>366000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>367000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>371000</v>
-      </c>
-      <c r="K96" s="3">
-        <v>349000</v>
       </c>
       <c r="L96" s="3">
         <v>349000</v>
       </c>
       <c r="M96" s="3">
+        <v>349000</v>
+      </c>
+      <c r="N96" s="3">
         <v>350000</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>356000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>343000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>345000</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-345000</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-349000</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-340000</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-341000</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-345000</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-353000</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-351000</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-352000</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-353000</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-357000</v>
-      </c>
-      <c r="AA96" s="3">
-        <v>-339000</v>
       </c>
       <c r="AB96" s="3">
         <v>-339000</v>
       </c>
       <c r="AC96" s="3">
+        <v>-339000</v>
+      </c>
+      <c r="AD96" s="3">
         <v>-340000</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-343000</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-335000</v>
-      </c>
-      <c r="AF96" s="3">
-        <v>-336000</v>
       </c>
       <c r="AG96" s="3">
         <v>-336000</v>
       </c>
       <c r="AH96" s="3">
+        <v>-336000</v>
+      </c>
+      <c r="AI96" s="3">
         <v>-340000</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>-331000</v>
-      </c>
-      <c r="AJ96" s="3">
-        <v>-330000</v>
       </c>
       <c r="AK96" s="3">
         <v>-330000</v>
       </c>
       <c r="AL96" s="3">
+        <v>-330000</v>
+      </c>
+      <c r="AM96" s="3">
         <v>-332000</v>
       </c>
-      <c r="AM96" s="3">
+      <c r="AN96" s="3">
         <v>-322000</v>
       </c>
-      <c r="AN96" s="3">
+      <c r="AO96" s="3">
         <v>-324000</v>
       </c>
-      <c r="AO96" s="3">
+      <c r="AP96" s="3">
         <v>-322000</v>
       </c>
-      <c r="AP96" s="3">
+      <c r="AQ96" s="3">
         <v>-321000</v>
       </c>
     </row>
-    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10438,8 +10674,11 @@
       <c r="AP97" s="3">
         <v>0</v>
       </c>
+      <c r="AQ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10560,8 +10799,11 @@
       <c r="AP98" s="3">
         <v>0</v>
       </c>
+      <c r="AQ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10682,370 +10924,382 @@
       <c r="AP99" s="3">
         <v>0</v>
       </c>
+      <c r="AQ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-1269000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-950000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-1661000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>1698000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-762000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-1125000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-2119000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>1122000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-1746000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>562000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-1164000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-1013000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-888000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-1424000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-2405000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-2003000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>583000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-1302000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>396000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-1783000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-2210000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-812000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-1848000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>664000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-253000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-645000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>973000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-693000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>199000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-630000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-567000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-775000</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-2216000</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>1567000</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-349000</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-527000</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>-585000</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>-858000</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>-232000</v>
       </c>
-      <c r="AP100" s="3">
+      <c r="AQ100" s="3">
         <v>-241000</v>
       </c>
     </row>
-    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>159000</v>
+      </c>
+      <c r="E101" s="3">
         <v>58000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-101000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>53000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-96000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-6000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>35000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-92000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>58000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-2000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>69000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-77000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-98000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-40000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>69000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-77000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-98000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-40000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-73000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-15000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>18000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-36000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>59000</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-9000</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>3000</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-45000</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-1000</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-17000</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>4000</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>34000</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-25000</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-2000</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>-63000</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>25000</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>-4000</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>-6000</v>
       </c>
-      <c r="AM101" s="3">
+      <c r="AN101" s="3">
         <v>28000</v>
       </c>
-      <c r="AN101" s="3">
+      <c r="AO101" s="3">
         <v>-17000</v>
       </c>
-      <c r="AO101" s="3">
+      <c r="AP101" s="3">
         <v>-67000</v>
       </c>
-      <c r="AP101" s="3">
+      <c r="AQ101" s="3">
         <v>18000</v>
       </c>
     </row>
-    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>119000</v>
+      </c>
+      <c r="E102" s="3">
         <v>164000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>16000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>83000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>121000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-299000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-129000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>110000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-83000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>30000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-157000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>403000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-7000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>255000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-137000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-4975000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>5325000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>103000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>15000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-202000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>157000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>5000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-37000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>164000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>51000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>12000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>57000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>221000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-25000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>53000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>183000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>56000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-1012000</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>1262000</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-342000</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>-226000</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>253000</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>78000</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>115000</v>
       </c>
-      <c r="AP102" s="3">
+      <c r="AQ102" s="3">
         <v>-141000</v>
       </c>
     </row>
